--- a/data/trans_dic/P36$fruta-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P36$fruta-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, fruta o zumo</t>
+          <t>Población que desayuna, al menos, fruta o zumo (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,78; 16,97</t>
+          <t>10,62; 17,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,39; 19,84</t>
+          <t>12,38; 20,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,41; 20,16</t>
+          <t>12,18; 19,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,8; 22,48</t>
+          <t>13,73; 22,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,51; 23,56</t>
+          <t>14,06; 23,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,76; 21,53</t>
+          <t>14,0; 22,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,69; 17,98</t>
+          <t>12,75; 17,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,21; 20,12</t>
+          <t>14,15; 19,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,87; 19,5</t>
+          <t>13,91; 19,62</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,11; 12,69</t>
+          <t>6,17; 12,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,49; 15,41</t>
+          <t>8,4; 15,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,95; 17,52</t>
+          <t>10,23; 17,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,49; 17,52</t>
+          <t>9,23; 16,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,66; 17,18</t>
+          <t>9,27; 17,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,44; 20,19</t>
+          <t>12,62; 20,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,63; 13,45</t>
+          <t>8,47; 13,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,96; 14,92</t>
+          <t>9,85; 14,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,18; 17,81</t>
+          <t>12,35; 17,92</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,38; 11,52</t>
+          <t>6,69; 11,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,79; 12,87</t>
+          <t>7,64; 12,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,73; 13,23</t>
+          <t>7,77; 13,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,41; 15,5</t>
+          <t>6,66; 16,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,16; 15,13</t>
+          <t>7,71; 15,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,67; 15,35</t>
+          <t>6,18; 15,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,02; 11,46</t>
+          <t>7,44; 11,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,42; 12,53</t>
+          <t>8,33; 12,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,08; 12,61</t>
+          <t>8,06; 12,56</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,46; 7,09</t>
+          <t>4,4; 7,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,03; 13,85</t>
+          <t>9,96; 13,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,35; 13,13</t>
+          <t>9,56; 13,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,99; 12,6</t>
+          <t>7,95; 12,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,86; 13,58</t>
+          <t>8,87; 13,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,25; 17,32</t>
+          <t>12,04; 17,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,08; 8,54</t>
+          <t>6,15; 8,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,02; 13,11</t>
+          <t>9,97; 12,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,07; 13,95</t>
+          <t>10,96; 14,04</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,31; 9,9</t>
+          <t>4,27; 10,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,34; 11,19</t>
+          <t>6,46; 11,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,48; 15,67</t>
+          <t>10,39; 16,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,54; 10,45</t>
+          <t>5,56; 10,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,23; 12,71</t>
+          <t>8,4; 13,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,13; 15,08</t>
+          <t>10,11; 14,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,79; 9,58</t>
+          <t>5,53; 9,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,99; 11,36</t>
+          <t>8,1; 11,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,71; 14,59</t>
+          <t>10,73; 14,47</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,89; 12,35</t>
+          <t>6,25; 12,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,4; 22,85</t>
+          <t>13,74; 22,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,42; 25,48</t>
+          <t>15,46; 25,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,6; 11,84</t>
+          <t>8,44; 11,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,11; 16,15</t>
+          <t>11,84; 16,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,32; 13,21</t>
+          <t>9,23; 13,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,61; 11,48</t>
+          <t>8,54; 11,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,85; 16,74</t>
+          <t>12,93; 16,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,29; 15,19</t>
+          <t>11,41; 15,24</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,25; 9,06</t>
+          <t>7,21; 9,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,98; 13,24</t>
+          <t>10,76; 13,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,81; 14,16</t>
+          <t>11,77; 14,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,58; 11,67</t>
+          <t>9,52; 11,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,5; 13,83</t>
+          <t>11,53; 13,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,11; 14,53</t>
+          <t>12,18; 14,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,67; 10,13</t>
+          <t>8,72; 10,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,42; 13,03</t>
+          <t>11,46; 13,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,25; 14,01</t>
+          <t>12,29; 13,95</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, fruta o zumo</t>
+          <t>Población que desayuna, al menos, fruta o zumo (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>50956; 80260</t>
+          <t>50198; 81656</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>54162; 86749</t>
+          <t>54117; 87739</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53245; 86489</t>
+          <t>52277; 82758</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42328; 68938</t>
+          <t>42101; 68738</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>42315; 73810</t>
+          <t>44058; 74140</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>47742; 74706</t>
+          <t>48574; 76443</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98932; 140154</t>
+          <t>99406; 139901</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>106622; 151001</t>
+          <t>106160; 149817</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>107675; 151335</t>
+          <t>107942; 152318</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22325; 46322</t>
+          <t>22526; 45478</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35380; 64238</t>
+          <t>35016; 64156</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37524; 66105</t>
+          <t>38583; 65772</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35196; 64949</t>
+          <t>34232; 59696</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32638; 58075</t>
+          <t>31347; 58338</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46164; 74942</t>
+          <t>46853; 75554</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>63486; 99008</t>
+          <t>62362; 97101</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>75164; 112648</t>
+          <t>74380; 113133</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>91142; 133301</t>
+          <t>92413; 134097</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>34462; 62253</t>
+          <t>36150; 62862</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>48860; 80769</t>
+          <t>47932; 81077</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40255; 68895</t>
+          <t>40492; 68565</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10762; 26014</t>
+          <t>11167; 27597</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18617; 39352</t>
+          <t>20063; 39742</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9421; 25506</t>
+          <t>10263; 25430</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49747; 81168</t>
+          <t>52653; 82498</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>74704; 111190</t>
+          <t>73972; 113258</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>55520; 86655</t>
+          <t>55371; 86279</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55152; 87678</t>
+          <t>54431; 89001</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>116130; 160426</t>
+          <t>115346; 160514</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>107441; 150853</t>
+          <t>109830; 153567</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56971; 89887</t>
+          <t>56678; 90607</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>67717; 103809</t>
+          <t>67792; 102960</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>101208; 143023</t>
+          <t>99414; 140927</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>118564; 166495</t>
+          <t>119916; 167376</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>192698; 252145</t>
+          <t>191588; 248845</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>218657; 275504</t>
+          <t>216321; 277236</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15117; 34704</t>
+          <t>14958; 35538</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>32315; 57050</t>
+          <t>32909; 57129</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64870; 96983</t>
+          <t>64297; 100707</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31408; 59212</t>
+          <t>31513; 58527</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>62454; 96398</t>
+          <t>63732; 98837</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>74750; 111357</t>
+          <t>74618; 109735</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>53153; 87884</t>
+          <t>50695; 85060</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>101322; 144128</t>
+          <t>102674; 143539</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>145379; 198039</t>
+          <t>145624; 196417</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17561; 36830</t>
+          <t>18652; 38447</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>35769; 60980</t>
+          <t>36663; 60541</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44282; 73158</t>
+          <t>44381; 72787</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>107349; 147856</t>
+          <t>105341; 149350</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>134326; 179184</t>
+          <t>131305; 179581</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>100680; 142697</t>
+          <t>99642; 142798</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>133225; 177525</t>
+          <t>132172; 177346</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>176906; 230400</t>
+          <t>177895; 229957</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>154327; 207653</t>
+          <t>156016; 208325</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>236584; 295672</t>
+          <t>235314; 297371</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>374931; 452209</t>
+          <t>367593; 448124</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>399333; 478833</t>
+          <t>397950; 476917</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>323180; 393661</t>
+          <t>321182; 396856</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>407545; 489991</t>
+          <t>408798; 486418</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>427201; 512669</t>
+          <t>429680; 510915</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>575751; 672350</t>
+          <t>578616; 676930</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>795129; 906858</t>
+          <t>797877; 918088</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>846464; 967891</t>
+          <t>848914; 964080</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$fruta-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P36$fruta-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,62; 17,27</t>
+          <t>10,32; 17,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,38; 20,07</t>
+          <t>12,51; 20,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,18; 19,29</t>
+          <t>12,74; 20,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,73; 22,41</t>
+          <t>13,65; 22,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,06; 23,66</t>
+          <t>13,69; 23,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,0; 22,03</t>
+          <t>13,52; 21,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,75; 17,95</t>
+          <t>12,77; 17,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,15; 19,96</t>
+          <t>14,06; 19,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,91; 19,62</t>
+          <t>13,83; 19,36</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,17; 12,45</t>
+          <t>6,08; 12,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,4; 15,39</t>
+          <t>8,59; 15,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,23; 17,44</t>
+          <t>10,61; 18,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,23; 16,1</t>
+          <t>9,2; 16,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,27; 17,26</t>
+          <t>9,56; 17,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,62; 20,36</t>
+          <t>12,35; 20,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,47; 13,19</t>
+          <t>8,37; 13,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,85; 14,99</t>
+          <t>9,68; 14,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,35; 17,92</t>
+          <t>12,39; 17,79</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,69; 11,63</t>
+          <t>6,57; 11,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,64; 12,92</t>
+          <t>7,87; 13,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,77; 13,16</t>
+          <t>7,51; 13,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,66; 16,45</t>
+          <t>6,08; 15,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,71; 15,28</t>
+          <t>7,17; 14,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,18; 15,31</t>
+          <t>6,18; 15,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,44; 11,65</t>
+          <t>7,03; 11,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,33; 12,76</t>
+          <t>8,28; 12,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,06; 12,56</t>
+          <t>7,97; 12,81</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,4; 7,2</t>
+          <t>4,43; 7,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,96; 13,86</t>
+          <t>9,84; 14,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,56; 13,37</t>
+          <t>9,22; 13,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,95; 12,7</t>
+          <t>7,81; 12,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,87; 13,46</t>
+          <t>8,84; 13,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,04; 17,06</t>
+          <t>12,18; 17,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,15; 8,59</t>
+          <t>6,11; 8,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,97; 12,94</t>
+          <t>10,02; 13,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,96; 14,04</t>
+          <t>11,0; 14,03</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,27; 10,14</t>
+          <t>4,37; 10,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,46; 11,21</t>
+          <t>6,24; 11,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,39; 16,27</t>
+          <t>10,48; 16,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,56; 10,33</t>
+          <t>5,67; 10,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,4; 13,03</t>
+          <t>8,02; 12,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,11; 14,86</t>
+          <t>10,22; 14,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,53; 9,27</t>
+          <t>5,63; 9,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,1; 11,32</t>
+          <t>8,02; 11,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,73; 14,47</t>
+          <t>10,88; 14,54</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,25; 12,89</t>
+          <t>6,06; 12,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,74; 22,68</t>
+          <t>13,43; 22,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,46; 25,35</t>
+          <t>16,01; 25,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,44; 11,96</t>
+          <t>8,41; 11,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,84; 16,19</t>
+          <t>11,98; 16,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,23; 13,22</t>
+          <t>9,27; 13,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,54; 11,46</t>
+          <t>8,52; 11,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,93; 16,71</t>
+          <t>12,89; 16,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,41; 15,24</t>
+          <t>11,24; 15,02</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,21; 9,11</t>
+          <t>7,16; 9,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,76; 13,12</t>
+          <t>10,99; 13,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,77; 14,1</t>
+          <t>11,9; 14,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,52; 11,76</t>
+          <t>9,71; 11,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,53; 13,73</t>
+          <t>11,56; 13,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,18; 14,48</t>
+          <t>12,22; 14,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,72; 10,2</t>
+          <t>8,63; 10,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,46; 13,19</t>
+          <t>11,5; 13,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,29; 13,95</t>
+          <t>12,26; 13,98</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>50198; 81656</t>
+          <t>48802; 82035</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>54117; 87739</t>
+          <t>54677; 87554</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52277; 82758</t>
+          <t>54670; 86128</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42101; 68738</t>
+          <t>41860; 68540</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>44058; 74140</t>
+          <t>42896; 72390</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48574; 76443</t>
+          <t>46934; 76313</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99406; 139901</t>
+          <t>99535; 138283</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>106160; 149817</t>
+          <t>105523; 149225</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>107942; 152318</t>
+          <t>107337; 150272</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22526; 45478</t>
+          <t>22214; 45552</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35016; 64156</t>
+          <t>35807; 63904</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38583; 65772</t>
+          <t>40033; 69985</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34232; 59696</t>
+          <t>34116; 59804</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31347; 58338</t>
+          <t>32298; 58259</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46853; 75554</t>
+          <t>45846; 75953</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62362; 97101</t>
+          <t>61575; 98163</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>74380; 113133</t>
+          <t>73087; 112888</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>92413; 134097</t>
+          <t>92759; 133136</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>36150; 62862</t>
+          <t>35496; 60718</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>47932; 81077</t>
+          <t>49413; 81829</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40492; 68565</t>
+          <t>39123; 67778</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11167; 27597</t>
+          <t>10202; 26502</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>20063; 39742</t>
+          <t>18645; 38975</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10263; 25430</t>
+          <t>10259; 25493</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>52653; 82498</t>
+          <t>49788; 82296</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>73972; 113258</t>
+          <t>73489; 113026</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>55371; 86279</t>
+          <t>54753; 88010</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>54431; 89001</t>
+          <t>54795; 88934</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>115346; 160514</t>
+          <t>113997; 162507</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>109830; 153567</t>
+          <t>105907; 150530</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56678; 90607</t>
+          <t>55730; 89781</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>67792; 102960</t>
+          <t>67566; 103357</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>99414; 140927</t>
+          <t>100620; 140403</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>119916; 167376</t>
+          <t>119061; 165278</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>191588; 248845</t>
+          <t>192645; 252514</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>216321; 277236</t>
+          <t>217092; 277015</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14958; 35538</t>
+          <t>15310; 35317</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>32909; 57129</t>
+          <t>31800; 56664</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64297; 100707</t>
+          <t>64862; 100152</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31513; 58527</t>
+          <t>32145; 57848</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>63732; 98837</t>
+          <t>60850; 98286</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>74618; 109735</t>
+          <t>75437; 109588</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50695; 85060</t>
+          <t>51618; 84621</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>102674; 143539</t>
+          <t>101659; 146456</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>145624; 196417</t>
+          <t>147624; 197384</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18652; 38447</t>
+          <t>18085; 37519</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>36663; 60541</t>
+          <t>35851; 60724</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44381; 72787</t>
+          <t>45965; 72357</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>105341; 149350</t>
+          <t>105036; 148469</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>131305; 179581</t>
+          <t>132912; 180717</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>99642; 142798</t>
+          <t>100113; 144441</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>132172; 177346</t>
+          <t>131750; 179537</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>177895; 229957</t>
+          <t>177370; 228620</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>156016; 208325</t>
+          <t>153612; 205323</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>235314; 297371</t>
+          <t>233613; 295568</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>367593; 448124</t>
+          <t>375366; 455875</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>397950; 476917</t>
+          <t>402316; 481441</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>321182; 396856</t>
+          <t>327788; 398673</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>408798; 486418</t>
+          <t>409811; 494137</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>429680; 510915</t>
+          <t>431015; 513868</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>578616; 676930</t>
+          <t>572637; 670261</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>797877; 918088</t>
+          <t>800326; 909954</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>848914; 964080</t>
+          <t>846956; 966368</t>
         </is>
       </c>
     </row>
